--- a/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/defects.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/defects.xlsx
@@ -485,12 +485,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -512,22 +512,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>User error</t>
+          <t>Code defect</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>User error</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>User error</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Integration failure</t>
+          <t>Code defect</t>
         </is>
       </c>
     </row>
@@ -647,17 +647,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Code defect</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Code defect</t>
         </is>
       </c>
     </row>
@@ -809,22 +809,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Vendor outage</t>
         </is>
       </c>
     </row>
@@ -836,22 +836,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vendor outage</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -890,22 +890,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vendor outage</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -944,22 +944,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Config error</t>
+          <t>User error</t>
         </is>
       </c>
     </row>
@@ -971,22 +971,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Config error</t>
+          <t>Data quality</t>
         </is>
       </c>
     </row>
@@ -998,22 +998,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1025,22 +1025,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Code defect</t>
+          <t>Data quality</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Permission</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Integration failure</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -1133,22 +1133,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vendor outage</t>
+          <t>Data quality</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Vendor outage</t>
         </is>
       </c>
     </row>
@@ -1187,22 +1187,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Vendor outage</t>
         </is>
       </c>
     </row>
@@ -1241,17 +1241,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Permission</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Vendor outage</t>
         </is>
       </c>
     </row>
@@ -1322,22 +1322,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Code defect</t>
+          <t>Data quality</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1349,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -1376,22 +1376,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Config error</t>
+          <t>Vendor outage</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Permission</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -1538,22 +1538,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vendor outage</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Code defect</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Code defect</t>
+          <t>Permission</t>
         </is>
       </c>
     </row>
@@ -1651,17 +1651,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Config error</t>
+          <t>Data quality</t>
         </is>
       </c>
     </row>
@@ -1700,22 +1700,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Code defect</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Vendor outage</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Permission</t>
         </is>
       </c>
     </row>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vendor outage</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Integration failure</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -1835,22 +1835,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Config error</t>
+          <t>Permission</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Vendor outage</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -1916,22 +1916,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>User error</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vendor outage</t>
+          <t>Data quality</t>
         </is>
       </c>
     </row>
@@ -1970,22 +1970,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Permission</t>
         </is>
       </c>
     </row>
@@ -1997,22 +1997,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Code defect</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Capacity</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Integration failure</t>
+          <t>Code defect</t>
         </is>
       </c>
     </row>
@@ -2078,22 +2078,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -2105,22 +2105,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Integration failure</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>Permission</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Code defect</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Code defect</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -2375,22 +2375,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Data quality</t>
         </is>
       </c>
     </row>
@@ -2456,22 +2456,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -2483,22 +2483,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Code defect</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Code defect</t>
+          <t>Vendor outage</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Config error</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Network</t>
+          <t>User error</t>
         </is>
       </c>
     </row>
@@ -2618,12 +2618,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Integration failure</t>
+          <t>User error</t>
         </is>
       </c>
     </row>
@@ -2645,17 +2645,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2677,17 +2677,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>User error</t>
         </is>
       </c>
     </row>
@@ -2699,22 +2699,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>User error</t>
         </is>
       </c>
     </row>
@@ -2726,22 +2726,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Data quality</t>
         </is>
       </c>
     </row>
@@ -2753,22 +2753,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vendor outage</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Config error</t>
         </is>
       </c>
     </row>
@@ -2807,22 +2807,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Integration failure</t>
         </is>
       </c>
     </row>
@@ -2844,12 +2844,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -2861,22 +2861,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>User error</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Code defect</t>
         </is>
       </c>
     </row>
